--- a/assets/floor_3_data.xlsx
+++ b/assets/floor_3_data.xlsx
@@ -70,9 +70,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -404,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -428,6 +427,9 @@
       <c r="G1" t="str">
         <v>LastAudit</v>
       </c>
+      <c r="H1" t="str">
+        <v>Color</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -451,6 +453,9 @@
       <c r="G2" t="str">
         <v/>
       </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -474,6 +479,9 @@
       <c r="G3" t="str">
         <v/>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -497,6 +505,9 @@
       <c r="G4" t="str">
         <v/>
       </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -520,17 +531,20 @@
       <c r="G5" t="str">
         <v/>
       </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -554,132 +568,228 @@
       <c r="G1" t="str">
         <v>LastAudit</v>
       </c>
+      <c r="H1" t="str">
+        <v>Color</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>WIFI-AP-Lobby</v>
+        <v>THMJNCHOTH01S05</v>
       </c>
       <c r="B2" t="str">
-        <v>AP</v>
+        <v>Switch</v>
       </c>
       <c r="C2">
-        <v>-800</v>
+        <v>-1111</v>
       </c>
       <c r="D2">
-        <v>1200</v>
+        <v>38</v>
       </c>
       <c r="E2" t="str">
-        <v>Main entrance access point</v>
+        <v>Office Switch</v>
       </c>
       <c r="F2" t="str">
         <v>Active</v>
       </c>
-      <c r="G2" s="1">
-        <v>44927</v>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>Orange</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>WIFI-AP-Canteen</v>
+        <v>AP09c</v>
       </c>
       <c r="B3" t="str">
         <v>AP</v>
       </c>
       <c r="C3">
-        <v>550</v>
+        <v>-2349</v>
       </c>
       <c r="D3">
-        <v>900</v>
+        <v>-413</v>
       </c>
       <c r="E3" t="str">
-        <v>Cafeteria coverage</v>
+        <v>Main entrance access point</v>
       </c>
       <c r="F3" t="str">
-        <v>Inactive</v>
+        <v>Active</v>
       </c>
       <c r="G3" t="str">
         <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>Salmon</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SRV-DC-01</v>
+        <v>AP10c</v>
       </c>
       <c r="B4" t="str">
-        <v>Server</v>
+        <v>AP</v>
       </c>
       <c r="C4">
-        <v>-1500</v>
+        <v>-1978</v>
       </c>
       <c r="D4">
-        <v>-1300</v>
+        <v>-393</v>
       </c>
       <c r="E4" t="str">
-        <v>Domain Controller 1</v>
+        <v>Cafeteria coverage</v>
       </c>
       <c r="F4" t="str">
         <v>Active</v>
       </c>
       <c r="G4" t="str">
         <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>Salmon</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SRV-FS-01</v>
+        <v>AP11c</v>
       </c>
       <c r="B5" t="str">
-        <v>Server</v>
+        <v>AP</v>
       </c>
       <c r="C5">
-        <v>-1550</v>
+        <v>-1841</v>
       </c>
       <c r="D5">
-        <v>-1300</v>
+        <v>113</v>
       </c>
       <c r="E5" t="str">
-        <v>File Server 1</v>
+        <v/>
       </c>
       <c r="F5" t="str">
         <v>Active</v>
       </c>
-      <c r="G5" s="1">
-        <v>44927</v>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>Salmon</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SW-IDF-01</v>
+        <v>AP12c</v>
       </c>
       <c r="B6" t="str">
-        <v>Switch</v>
+        <v>AP</v>
       </c>
       <c r="C6">
-        <v>-1450</v>
+        <v>-2010</v>
       </c>
       <c r="D6">
-        <v>-1350</v>
+        <v>172</v>
       </c>
       <c r="E6" t="str">
-        <v>Main Distribution Frame Switch</v>
+        <v/>
       </c>
       <c r="F6" t="str">
         <v>Active</v>
       </c>
       <c r="G6" t="str">
         <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>Salmon</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AP13c</v>
+      </c>
+      <c r="B7" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C7">
+        <v>-2548</v>
+      </c>
+      <c r="D7">
+        <v>574</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>Salmon</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AP14c</v>
+      </c>
+      <c r="B8" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C8">
+        <v>-2200</v>
+      </c>
+      <c r="D8">
+        <v>676</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>Salmon</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AP15c</v>
+      </c>
+      <c r="B9" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C9">
+        <v>-2383</v>
+      </c>
+      <c r="D9">
+        <v>286</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>Salmon</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -703,6 +813,9 @@
       <c r="G1" t="str">
         <v>LastAudit</v>
       </c>
+      <c r="H1" t="str">
+        <v>Color</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -726,6 +839,9 @@
       <c r="G2" t="str">
         <v/>
       </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -749,6 +865,9 @@
       <c r="G3" t="str">
         <v/>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -772,17 +891,20 @@
       <c r="G4" t="str">
         <v/>
       </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -806,6 +928,9 @@
       <c r="G1" t="str">
         <v>LastAudit</v>
       </c>
+      <c r="H1" t="str">
+        <v>Color</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -829,17 +954,20 @@
       <c r="G2" t="str">
         <v>2025-12-15</v>
       </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -863,6 +991,9 @@
       <c r="G1" t="str">
         <v>LastAudit</v>
       </c>
+      <c r="H1" t="str">
+        <v>Color</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -886,6 +1017,9 @@
       <c r="G2" t="str">
         <v/>
       </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -909,6 +1043,9 @@
       <c r="G3" t="str">
         <v/>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -932,6 +1069,9 @@
       <c r="G4" t="str">
         <v/>
       </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -955,17 +1095,20 @@
       <c r="G5" t="str">
         <v>2025-12-15</v>
       </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -989,6 +1132,9 @@
       <c r="G1" t="str">
         <v>LastAudit</v>
       </c>
+      <c r="H1" t="str">
+        <v>Color</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1012,6 +1158,9 @@
       <c r="G2" t="str">
         <v/>
       </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1035,6 +1184,9 @@
       <c r="G3" t="str">
         <v/>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1058,17 +1210,20 @@
       <c r="G4" t="str">
         <v/>
       </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1092,6 +1247,9 @@
       <c r="G1" t="str">
         <v>LastAudit</v>
       </c>
+      <c r="H1" t="str">
+        <v>Color</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1115,6 +1273,9 @@
       <c r="G2" t="str">
         <v>2025-12-15</v>
       </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1138,10 +1299,13 @@
       <c r="G3" t="str">
         <v>2025-12-15</v>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/assets/floor_3_data.xlsx
+++ b/assets/floor_3_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788F1889-D547-4B27-9C74-5FC16A333DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6578D9-28BF-4A4E-AD65-BA342430078A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loc_name" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="44">
   <si>
     <t>Name</t>
   </si>
@@ -107,24 +107,6 @@
   </si>
   <si>
     <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>Vitamin A</t>
-  </si>
-  <si>
-    <t>Analog Scale</t>
-  </si>
-  <si>
-    <t>Vitamin B</t>
-  </si>
-  <si>
-    <t>Digital Scale</t>
-  </si>
-  <si>
-    <t>Vitamin C</t>
-  </si>
-  <si>
-    <t>ttt</t>
   </si>
   <si>
     <t>ccc</t>
@@ -589,7 +571,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C2">
         <v>-2036</v>
@@ -600,7 +582,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C3">
         <v>-2194</v>
@@ -611,7 +593,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C4">
         <v>-1129</v>
@@ -832,7 +814,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -859,89 +841,6 @@
       </c>
       <c r="H1" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2">
-        <v>1245</v>
-      </c>
-      <c r="D2">
-        <v>-282</v>
-      </c>
-      <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3">
-        <v>1365</v>
-      </c>
-      <c r="D3">
-        <v>-149</v>
-      </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4">
-        <v>1503</v>
-      </c>
-      <c r="D4">
-        <v>-25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5">
-        <v>-660</v>
-      </c>
-      <c r="D5">
-        <v>-538</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -982,10 +881,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>1688</v>
@@ -1005,10 +904,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>18</v>
@@ -1045,25 +944,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F1" t="s">
         <v>7</v>
       </c>
       <c r="G1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="I1" t="s">
         <v>4</v>
@@ -1071,7 +970,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B2">
         <v>-2126</v>
@@ -1086,7 +985,7 @@
         <v>1314</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G2">
         <v>0.2</v>
@@ -1097,7 +996,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>-1752</v>
@@ -1112,7 +1011,7 @@
         <v>731</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G3">
         <v>0.2</v>
@@ -1123,7 +1022,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B4">
         <v>-2673</v>
@@ -1138,7 +1037,7 @@
         <v>731</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G4">
         <v>0.2</v>
@@ -1161,7 +1060,7 @@
         <v>1314</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G5">
         <v>0.2</v>

--- a/assets/floor_3_data.xlsx
+++ b/assets/floor_3_data.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6578D9-28BF-4A4E-AD65-BA342430078A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE242E3-6DAF-4953-9611-DD1B163D0278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loc_name" sheetId="1" r:id="rId1"/>
     <sheet name="it_dev" sheetId="2" r:id="rId2"/>
-    <sheet name="weight" sheetId="5" r:id="rId3"/>
-    <sheet name="clock" sheetId="7" r:id="rId4"/>
-    <sheet name="zones" sheetId="8" r:id="rId5"/>
+    <sheet name="prod_comp" sheetId="9" r:id="rId3"/>
+    <sheet name="weight" sheetId="5" r:id="rId4"/>
+    <sheet name="clock" sheetId="7" r:id="rId5"/>
+    <sheet name="zones" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="48">
   <si>
     <t>Name</t>
   </si>
@@ -161,6 +162,18 @@
   </si>
   <si>
     <t>Switch Room</t>
+  </si>
+  <si>
+    <t>GWINS</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Gw-rtd-1</t>
+  </si>
+  <si>
+    <t>Gw-rtd-2</t>
   </si>
 </sst>
 </file>
@@ -813,6 +826,88 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{680E1512-5F3C-417C-802D-7FFDB1BDE4BD}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2">
+        <v>-2592</v>
+      </c>
+      <c r="D2">
+        <v>-570</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3">
+        <v>-2326</v>
+      </c>
+      <c r="D3">
+        <v>-414</v>
+      </c>
+      <c r="E3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -848,7 +943,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -930,7 +1025,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>

--- a/assets/floor_3_data.xlsx
+++ b/assets/floor_3_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE242E3-6DAF-4953-9611-DD1B163D0278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6FD198-E511-42EE-B564-296BD3E84027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loc_name" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="weight" sheetId="5" r:id="rId4"/>
     <sheet name="clock" sheetId="7" r:id="rId5"/>
     <sheet name="zones" sheetId="8" r:id="rId6"/>
+    <sheet name="building" sheetId="10" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="51">
   <si>
     <t>Name</t>
   </si>
@@ -174,6 +175,15 @@
   </si>
   <si>
     <t>Gw-rtd-2</t>
+  </si>
+  <si>
+    <t>#55ab46</t>
+  </si>
+  <si>
+    <t>RTD f3</t>
+  </si>
+  <si>
+    <t>Enfa f3</t>
   </si>
 </sst>
 </file>
@@ -1167,4 +1177,100 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02D7B8DF-5E23-4189-9042-FFD891F56808}">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.44140625" customWidth="1"/>
+    <col min="8" max="8" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2">
+        <v>-2703</v>
+      </c>
+      <c r="C2">
+        <v>-584</v>
+      </c>
+      <c r="D2">
+        <v>-1785</v>
+      </c>
+      <c r="E2">
+        <v>1308</v>
+      </c>
+      <c r="F2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2">
+        <v>0.2</v>
+      </c>
+      <c r="H2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3">
+        <v>-1782</v>
+      </c>
+      <c r="C3">
+        <v>-194</v>
+      </c>
+      <c r="D3">
+        <v>-471</v>
+      </c>
+      <c r="E3">
+        <v>930</v>
+      </c>
+      <c r="F3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3">
+        <v>0.2</v>
+      </c>
+      <c r="H3">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/assets/floor_3_data.xlsx
+++ b/assets/floor_3_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6FD198-E511-42EE-B564-296BD3E84027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CAED547-8314-4096-921F-3DCBBF9FA842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loc_name" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,17 @@
     <sheet name="zones" sheetId="8" r:id="rId6"/>
     <sheet name="building" sheetId="10" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -1223,13 +1232,13 @@
         <v>49</v>
       </c>
       <c r="B2">
-        <v>-2703</v>
+        <v>-2667</v>
       </c>
       <c r="C2">
         <v>-584</v>
       </c>
       <c r="D2">
-        <v>-1785</v>
+        <v>-1749</v>
       </c>
       <c r="E2">
         <v>1308</v>
@@ -1249,13 +1258,13 @@
         <v>50</v>
       </c>
       <c r="B3">
-        <v>-1782</v>
+        <v>-1746</v>
       </c>
       <c r="C3">
         <v>-194</v>
       </c>
       <c r="D3">
-        <v>-471</v>
+        <v>-435</v>
       </c>
       <c r="E3">
         <v>930</v>
